--- a/Reports/01_Chart_of_Accounts/شجرة_الحسابات_المحدّثة_المقسّمة.xlsx
+++ b/Reports/01_Chart_of_Accounts/شجرة_الحسابات_المحدّثة_المقسّمة.xlsx
@@ -2360,7 +2360,7 @@
         </is>
       </c>
       <c r="G51" s="16" t="n">
-        <v>10090610.74</v>
+        <v>10086332.68</v>
       </c>
     </row>
     <row r="52">
@@ -2430,7 +2430,7 @@
         </is>
       </c>
       <c r="G53" s="16" t="n">
-        <v>28815.4</v>
+        <v>33093.46</v>
       </c>
     </row>
     <row r="54">
@@ -12181,7 +12181,7 @@
       </c>
       <c r="D332" s="17" t="inlineStr">
         <is>
-          <t>بونص الموظفين - Staff Bonus</t>
+          <t>بدل أكل / بوفيه الموظفين - Staff Meals (Food &amp; Buffet)</t>
         </is>
       </c>
       <c r="E332" s="19" t="inlineStr">
@@ -12195,7 +12195,7 @@
         </is>
       </c>
       <c r="G332" s="20" t="n">
-        <v>73284</v>
+        <v>40727.09</v>
       </c>
     </row>
     <row r="333">
@@ -12211,61 +12211,61 @@
       </c>
       <c r="C333" s="14" t="inlineStr">
         <is>
+          <t>500303</t>
+        </is>
+      </c>
+      <c r="D333" s="13" t="inlineStr">
+        <is>
+          <t>بونص الموظفين - Staff Bonus</t>
+        </is>
+      </c>
+      <c r="E333" s="15" t="inlineStr">
+        <is>
+          <t>عادي</t>
+        </is>
+      </c>
+      <c r="F333" s="15" t="inlineStr">
+        <is>
+          <t>نشط</t>
+        </is>
+      </c>
+      <c r="G333" s="16" t="n">
+        <v>73284</v>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" s="17" t="inlineStr">
+        <is>
+          <t>المصروفات</t>
+        </is>
+      </c>
+      <c r="B334" s="17" t="inlineStr">
+        <is>
+          <t>المصروفات التشغيلية</t>
+        </is>
+      </c>
+      <c r="C334" s="18" t="inlineStr">
+        <is>
           <t>500304</t>
         </is>
       </c>
-      <c r="D333" s="13" t="inlineStr">
+      <c r="D334" s="17" t="inlineStr">
         <is>
           <t>تذاكر السفر - Travel Tickets</t>
         </is>
       </c>
-      <c r="E333" s="15" t="inlineStr">
-        <is>
-          <t>عادي</t>
-        </is>
-      </c>
-      <c r="F333" s="15" t="inlineStr">
-        <is>
-          <t>نشط</t>
-        </is>
-      </c>
-      <c r="G333" s="16" t="n">
+      <c r="E334" s="19" t="inlineStr">
+        <is>
+          <t>عادي</t>
+        </is>
+      </c>
+      <c r="F334" s="19" t="inlineStr">
+        <is>
+          <t>نشط</t>
+        </is>
+      </c>
+      <c r="G334" s="20" t="n">
         <v>113822</v>
-      </c>
-    </row>
-    <row r="334">
-      <c r="A334" s="4" t="inlineStr">
-        <is>
-          <t>المصروفات</t>
-        </is>
-      </c>
-      <c r="B334" s="4" t="inlineStr">
-        <is>
-          <t>المصروفات التشغيلية</t>
-        </is>
-      </c>
-      <c r="C334" s="5" t="inlineStr">
-        <is>
-          <t>500305</t>
-        </is>
-      </c>
-      <c r="D334" s="4" t="inlineStr">
-        <is>
-          <t>Accommodation Rent For Staff</t>
-        </is>
-      </c>
-      <c r="E334" s="6" t="inlineStr">
-        <is>
-          <t>عادي</t>
-        </is>
-      </c>
-      <c r="F334" s="6" t="inlineStr">
-        <is>
-          <t>مؤرشف</t>
-        </is>
-      </c>
-      <c r="G334" s="7" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="335">
@@ -12281,61 +12281,61 @@
       </c>
       <c r="C335" s="5" t="inlineStr">
         <is>
+          <t>500305</t>
+        </is>
+      </c>
+      <c r="D335" s="4" t="inlineStr">
+        <is>
+          <t>Accommodation Rent For Staff</t>
+        </is>
+      </c>
+      <c r="E335" s="6" t="inlineStr">
+        <is>
+          <t>عادي</t>
+        </is>
+      </c>
+      <c r="F335" s="6" t="inlineStr">
+        <is>
+          <t>مؤرشف</t>
+        </is>
+      </c>
+      <c r="G335" s="7" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" s="4" t="inlineStr">
+        <is>
+          <t>المصروفات</t>
+        </is>
+      </c>
+      <c r="B336" s="4" t="inlineStr">
+        <is>
+          <t>المصروفات التشغيلية</t>
+        </is>
+      </c>
+      <c r="C336" s="5" t="inlineStr">
+        <is>
           <t>500306</t>
         </is>
       </c>
-      <c r="D335" s="4" t="inlineStr">
+      <c r="D336" s="4" t="inlineStr">
         <is>
           <t>Accommodation Expenses for Staff</t>
         </is>
       </c>
-      <c r="E335" s="6" t="inlineStr">
-        <is>
-          <t>عادي</t>
-        </is>
-      </c>
-      <c r="F335" s="6" t="inlineStr">
+      <c r="E336" s="6" t="inlineStr">
+        <is>
+          <t>عادي</t>
+        </is>
+      </c>
+      <c r="F336" s="6" t="inlineStr">
         <is>
           <t>مؤرشف</t>
         </is>
       </c>
-      <c r="G335" s="7" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="336">
-      <c r="A336" s="17" t="inlineStr">
-        <is>
-          <t>المصروفات</t>
-        </is>
-      </c>
-      <c r="B336" s="17" t="inlineStr">
-        <is>
-          <t>المصروفات التشغيلية</t>
-        </is>
-      </c>
-      <c r="C336" s="18" t="inlineStr">
-        <is>
-          <t>500307</t>
-        </is>
-      </c>
-      <c r="D336" s="17" t="inlineStr">
-        <is>
-          <t>مصاريف موظفين أخرى (طبية/عمالة/عمولة) - Other Staff Costs</t>
-        </is>
-      </c>
-      <c r="E336" s="19" t="inlineStr">
-        <is>
-          <t>عادي</t>
-        </is>
-      </c>
-      <c r="F336" s="19" t="inlineStr">
-        <is>
-          <t>نشط</t>
-        </is>
-      </c>
-      <c r="G336" s="20" t="n">
-        <v>56039.49</v>
+      <c r="G336" s="7" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="337">
@@ -12351,61 +12351,61 @@
       </c>
       <c r="C337" s="14" t="inlineStr">
         <is>
+          <t>500307</t>
+        </is>
+      </c>
+      <c r="D337" s="13" t="inlineStr">
+        <is>
+          <t>مصاريف موظفين أخرى (طبية/عمالة/عمولة) - Other Staff Costs</t>
+        </is>
+      </c>
+      <c r="E337" s="15" t="inlineStr">
+        <is>
+          <t>عادي</t>
+        </is>
+      </c>
+      <c r="F337" s="15" t="inlineStr">
+        <is>
+          <t>نشط</t>
+        </is>
+      </c>
+      <c r="G337" s="16" t="n">
+        <v>56039.49</v>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" s="17" t="inlineStr">
+        <is>
+          <t>المصروفات</t>
+        </is>
+      </c>
+      <c r="B338" s="17" t="inlineStr">
+        <is>
+          <t>المصروفات التشغيلية</t>
+        </is>
+      </c>
+      <c r="C338" s="18" t="inlineStr">
+        <is>
           <t>500308</t>
         </is>
       </c>
-      <c r="D337" s="13" t="inlineStr">
+      <c r="D338" s="17" t="inlineStr">
         <is>
           <t>إقامات وتأشيرات - Residence &amp; Visa</t>
         </is>
       </c>
-      <c r="E337" s="15" t="inlineStr">
-        <is>
-          <t>عادي</t>
-        </is>
-      </c>
-      <c r="F337" s="15" t="inlineStr">
-        <is>
-          <t>نشط</t>
-        </is>
-      </c>
-      <c r="G337" s="16" t="n">
+      <c r="E338" s="19" t="inlineStr">
+        <is>
+          <t>عادي</t>
+        </is>
+      </c>
+      <c r="F338" s="19" t="inlineStr">
+        <is>
+          <t>نشط</t>
+        </is>
+      </c>
+      <c r="G338" s="20" t="n">
         <v>207752.25</v>
-      </c>
-    </row>
-    <row r="338">
-      <c r="A338" s="4" t="inlineStr">
-        <is>
-          <t>المصروفات</t>
-        </is>
-      </c>
-      <c r="B338" s="4" t="inlineStr">
-        <is>
-          <t>المصروفات التشغيلية</t>
-        </is>
-      </c>
-      <c r="C338" s="5" t="inlineStr">
-        <is>
-          <t>500309</t>
-        </is>
-      </c>
-      <c r="D338" s="4" t="inlineStr">
-        <is>
-          <t>ID Renewal Expenses</t>
-        </is>
-      </c>
-      <c r="E338" s="6" t="inlineStr">
-        <is>
-          <t>عادي</t>
-        </is>
-      </c>
-      <c r="F338" s="6" t="inlineStr">
-        <is>
-          <t>مؤرشف</t>
-        </is>
-      </c>
-      <c r="G338" s="7" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="339">
@@ -12421,12 +12421,12 @@
       </c>
       <c r="C339" s="5" t="inlineStr">
         <is>
-          <t>500310</t>
+          <t>500309</t>
         </is>
       </c>
       <c r="D339" s="4" t="inlineStr">
         <is>
-          <t>Food Allowance</t>
+          <t>ID Renewal Expenses</t>
         </is>
       </c>
       <c r="E339" s="6" t="inlineStr">
@@ -12456,12 +12456,12 @@
       </c>
       <c r="C340" s="5" t="inlineStr">
         <is>
-          <t>500311</t>
+          <t>500310</t>
         </is>
       </c>
       <c r="D340" s="4" t="inlineStr">
         <is>
-          <t>Salaries Bonus</t>
+          <t>Food Allowance</t>
         </is>
       </c>
       <c r="E340" s="6" t="inlineStr">
@@ -12491,131 +12491,131 @@
       </c>
       <c r="C341" s="5" t="inlineStr">
         <is>
+          <t>500311</t>
+        </is>
+      </c>
+      <c r="D341" s="4" t="inlineStr">
+        <is>
+          <t>Salaries Bonus</t>
+        </is>
+      </c>
+      <c r="E341" s="6" t="inlineStr">
+        <is>
+          <t>عادي</t>
+        </is>
+      </c>
+      <c r="F341" s="6" t="inlineStr">
+        <is>
+          <t>مؤرشف</t>
+        </is>
+      </c>
+      <c r="G341" s="7" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342" s="4" t="inlineStr">
+        <is>
+          <t>المصروفات</t>
+        </is>
+      </c>
+      <c r="B342" s="4" t="inlineStr">
+        <is>
+          <t>المصروفات التشغيلية</t>
+        </is>
+      </c>
+      <c r="C342" s="5" t="inlineStr">
+        <is>
           <t>500312</t>
         </is>
       </c>
-      <c r="D341" s="4" t="inlineStr">
+      <c r="D342" s="4" t="inlineStr">
         <is>
           <t>Mobile Bill Allowance</t>
         </is>
       </c>
-      <c r="E341" s="6" t="inlineStr">
-        <is>
-          <t>عادي</t>
-        </is>
-      </c>
-      <c r="F341" s="6" t="inlineStr">
+      <c r="E342" s="6" t="inlineStr">
+        <is>
+          <t>عادي</t>
+        </is>
+      </c>
+      <c r="F342" s="6" t="inlineStr">
         <is>
           <t>مؤرشف</t>
         </is>
       </c>
-      <c r="G341" s="7" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="342">
-      <c r="A342" s="17" t="inlineStr">
+      <c r="G342" s="7" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343" s="13" t="inlineStr">
         <is>
           <t>المصروفات</t>
         </is>
       </c>
-      <c r="B342" s="17" t="inlineStr">
+      <c r="B343" s="13" t="inlineStr">
         <is>
           <t>المصروفات التشغيلية</t>
         </is>
       </c>
-      <c r="C342" s="18" t="inlineStr">
+      <c r="C343" s="14" t="inlineStr">
         <is>
           <t>500909</t>
         </is>
       </c>
-      <c r="D342" s="17" t="inlineStr">
+      <c r="D343" s="13" t="inlineStr">
         <is>
           <t>خسائر فروقات نقدية - Cash Difference Loss</t>
         </is>
       </c>
-      <c r="E342" s="19" t="inlineStr">
-        <is>
-          <t>عادي</t>
-        </is>
-      </c>
-      <c r="F342" s="19" t="inlineStr">
-        <is>
-          <t>نشط</t>
-        </is>
-      </c>
-      <c r="G342" s="20" t="n">
+      <c r="E343" s="15" t="inlineStr">
+        <is>
+          <t>عادي</t>
+        </is>
+      </c>
+      <c r="F343" s="15" t="inlineStr">
+        <is>
+          <t>نشط</t>
+        </is>
+      </c>
+      <c r="G343" s="16" t="n">
         <v>37343.47</v>
       </c>
     </row>
-    <row r="343">
-      <c r="A343" s="4" t="inlineStr">
+    <row r="344">
+      <c r="A344" s="4" t="inlineStr">
         <is>
           <t>المصروفات</t>
         </is>
       </c>
-      <c r="B343" s="4" t="inlineStr">
+      <c r="B344" s="4" t="inlineStr">
         <is>
           <t>المصروفات التشغيلية</t>
         </is>
       </c>
-      <c r="C343" s="5" t="inlineStr">
+      <c r="C344" s="5" t="inlineStr">
         <is>
           <t>501108</t>
         </is>
       </c>
-      <c r="D343" s="4" t="inlineStr">
+      <c r="D344" s="4" t="inlineStr">
         <is>
           <t>Scrap Expenses</t>
         </is>
       </c>
-      <c r="E343" s="6" t="inlineStr">
-        <is>
-          <t>عادي</t>
-        </is>
-      </c>
-      <c r="F343" s="6" t="inlineStr">
+      <c r="E344" s="6" t="inlineStr">
+        <is>
+          <t>عادي</t>
+        </is>
+      </c>
+      <c r="F344" s="6" t="inlineStr">
         <is>
           <t>مؤرشف</t>
         </is>
       </c>
-      <c r="G343" s="7" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="344">
-      <c r="A344" s="17" t="inlineStr">
-        <is>
-          <t>المصروفات</t>
-        </is>
-      </c>
-      <c r="B344" s="17" t="inlineStr">
-        <is>
-          <t>المصروفات التشغيلية</t>
-        </is>
-      </c>
-      <c r="C344" s="18" t="inlineStr">
-        <is>
-          <t>502002</t>
-        </is>
-      </c>
-      <c r="D344" s="17" t="inlineStr">
-        <is>
-          <t>خصومات مسموح بها - Discounts Allowed</t>
-        </is>
-      </c>
-      <c r="E344" s="19" t="inlineStr">
-        <is>
-          <t>عادي</t>
-        </is>
-      </c>
-      <c r="F344" s="19" t="inlineStr">
-        <is>
-          <t>نشط</t>
-        </is>
-      </c>
-      <c r="G344" s="20" t="n">
-        <v>2755.07</v>
+      <c r="G344" s="7" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="345">
@@ -12631,12 +12631,12 @@
       </c>
       <c r="C345" s="14" t="inlineStr">
         <is>
-          <t>502003</t>
+          <t>502002</t>
         </is>
       </c>
       <c r="D345" s="13" t="inlineStr">
         <is>
-          <t>مصروفات قانونية - Legal Expenses</t>
+          <t>خصومات مسموح بها - Discounts Allowed</t>
         </is>
       </c>
       <c r="E345" s="15" t="inlineStr">
@@ -12650,7 +12650,7 @@
         </is>
       </c>
       <c r="G345" s="16" t="n">
-        <v>138600</v>
+        <v>2755.07</v>
       </c>
     </row>
     <row r="346">
@@ -12666,12 +12666,12 @@
       </c>
       <c r="C346" s="18" t="inlineStr">
         <is>
-          <t>502004</t>
+          <t>502003</t>
         </is>
       </c>
       <c r="D346" s="17" t="inlineStr">
         <is>
-          <t>ديون معدومة - Bad Debts</t>
+          <t>مصروفات قانونية - Legal Expenses</t>
         </is>
       </c>
       <c r="E346" s="19" t="inlineStr">
@@ -12685,7 +12685,7 @@
         </is>
       </c>
       <c r="G346" s="20" t="n">
-        <v>432</v>
+        <v>138600</v>
       </c>
     </row>
     <row r="347">
@@ -12701,12 +12701,12 @@
       </c>
       <c r="C347" s="14" t="inlineStr">
         <is>
-          <t>502005</t>
+          <t>502004</t>
         </is>
       </c>
       <c r="D347" s="13" t="inlineStr">
         <is>
-          <t>المصاريف والرسوم البنكية العامة - Bank Charges &amp; Fees (General)</t>
+          <t>ديون معدومة - Bad Debts</t>
         </is>
       </c>
       <c r="E347" s="15" t="inlineStr">
@@ -12720,7 +12720,7 @@
         </is>
       </c>
       <c r="G347" s="16" t="n">
-        <v>125842.81</v>
+        <v>432</v>
       </c>
     </row>
     <row r="348">
@@ -12736,12 +12736,12 @@
       </c>
       <c r="C348" s="18" t="inlineStr">
         <is>
-          <t>502006</t>
+          <t>502005</t>
         </is>
       </c>
       <c r="D348" s="17" t="inlineStr">
         <is>
-          <t>إيجار المحلات - Shops Rent</t>
+          <t>المصاريف والرسوم البنكية العامة - Bank Charges &amp; Fees (General)</t>
         </is>
       </c>
       <c r="E348" s="19" t="inlineStr">
@@ -12755,7 +12755,7 @@
         </is>
       </c>
       <c r="G348" s="20" t="n">
-        <v>4104859</v>
+        <v>125842.81</v>
       </c>
     </row>
     <row r="349">
@@ -12771,12 +12771,12 @@
       </c>
       <c r="C349" s="14" t="inlineStr">
         <is>
-          <t>502007</t>
+          <t>502006</t>
         </is>
       </c>
       <c r="D349" s="13" t="inlineStr">
         <is>
-          <t>مطبوعات وقرطاسية - Printing &amp; Stationery Expenses</t>
+          <t>إيجار المحلات - Shops Rent</t>
         </is>
       </c>
       <c r="E349" s="15" t="inlineStr">
@@ -12790,7 +12790,7 @@
         </is>
       </c>
       <c r="G349" s="16" t="n">
-        <v>36171.75</v>
+        <v>4104859</v>
       </c>
     </row>
     <row r="350">
@@ -12806,12 +12806,12 @@
       </c>
       <c r="C350" s="18" t="inlineStr">
         <is>
-          <t>502008</t>
+          <t>502007</t>
         </is>
       </c>
       <c r="D350" s="17" t="inlineStr">
         <is>
-          <t>بدل أكل / بوفيه الموظفين - Staff Meals (Food &amp; Buffet)</t>
+          <t>مطبوعات وقرطاسية - Printing &amp; Stationery Expenses</t>
         </is>
       </c>
       <c r="E350" s="19" t="inlineStr">
@@ -12825,7 +12825,7 @@
         </is>
       </c>
       <c r="G350" s="20" t="n">
-        <v>40727.09</v>
+        <v>36171.75</v>
       </c>
     </row>
     <row r="351">
